--- a/Assignment 1/reports.xlsx
+++ b/Assignment 1/reports.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yohan\Documents\UiPath\SalesOrderEntry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/476c497ce194b01b/Desktop/UOM/Course/Y3/RPA/Assignment 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8764CC3-E326-4C97-92AB-98690B73087F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{F8764CC3-E326-4C97-92AB-98690B73087F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A45E6E04-F2B0-4E0E-B49A-AFAC78DAD591}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{C1934DC9-55F9-4D88-8887-3B5A3C0E9A4B}"/>
+    <workbookView xWindow="2784" yWindow="1956" windowWidth="17280" windowHeight="8880" xr2:uid="{C1934DC9-55F9-4D88-8887-3B5A3C0E9A4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>Invoice Number</t>
   </si>
@@ -60,16 +60,28 @@
   </si>
   <si>
     <t>INV-2026-999</t>
+  </si>
+  <si>
+    <t>Test Item2</t>
+  </si>
+  <si>
+    <t>INV-2026-001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -432,14 +444,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4BDFCC-78EE-44B2-BA2D-BE923DCCAAD1}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -453,7 +465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -467,7 +479,22 @@
         <v>5</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>46287</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
